--- a/output/graficos_regionales_indicadores/plot_regional_p_basica_a_2021_antofagasta.xlsx
+++ b/output/graficos_regionales_indicadores/plot_regional_p_basica_a_2021_antofagasta.xlsx
@@ -85,7 +85,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 18:30</t>
+    <t xml:space="preserve">2026-09-09 19:28</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_indicadores/plot_regional_p_basica_a_2021_antofagasta.xlsx
+++ b/output/graficos_regionales_indicadores/plot_regional_p_basica_a_2021_antofagasta.xlsx
@@ -85,7 +85,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 19:28</t>
+    <t xml:space="preserve">2026-09-18 09:31</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_indicadores/plot_regional_p_basica_a_2021_antofagasta.xlsx
+++ b/output/graficos_regionales_indicadores/plot_regional_p_basica_a_2021_antofagasta.xlsx
@@ -85,7 +85,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 09:31</t>
+    <t xml:space="preserve">2026-10-05 06:58</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
